--- a/public/menu.xlsx
+++ b/public/menu.xlsx
@@ -1271,7 +1271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1335,9 +1335,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2295,7 +2292,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="33" t="s">
+      <c r="A50" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B50" s="29" t="s">
@@ -2306,7 +2303,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="33" t="s">
+      <c r="A51" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B51" s="31" t="s">
@@ -2317,7 +2314,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="33" t="s">
+      <c r="A52" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B52" s="29" t="s">
@@ -2328,7 +2325,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="33" t="s">
+      <c r="A53" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B53" s="31" t="s">
@@ -2339,7 +2336,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="33" t="s">
+      <c r="A54" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B54" s="29" t="s">
@@ -2350,7 +2347,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="33" t="s">
+      <c r="A55" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B55" s="31" t="s">
@@ -2364,10 +2361,10 @@
       <c r="A56" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B56" s="34" t="s">
+      <c r="B56" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C56" s="35">
+      <c r="C56" s="34">
         <v>10.99</v>
       </c>
     </row>
@@ -2375,10 +2372,10 @@
       <c r="A57" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B57" s="36" t="s">
+      <c r="B57" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C57" s="37">
+      <c r="C57" s="36">
         <v>11.99</v>
       </c>
     </row>
@@ -2386,10 +2383,10 @@
       <c r="A58" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="34" t="s">
+      <c r="B58" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="35">
+      <c r="C58" s="34">
         <v>4.99</v>
       </c>
     </row>
@@ -2397,10 +2394,10 @@
       <c r="A59" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B59" s="36" t="s">
+      <c r="B59" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C59" s="37">
+      <c r="C59" s="36">
         <v>4.99</v>
       </c>
     </row>
@@ -2408,10 +2405,10 @@
       <c r="A60" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B60" s="34" t="s">
+      <c r="B60" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="C60" s="35">
+      <c r="C60" s="34">
         <v>4.99</v>
       </c>
     </row>
@@ -2419,10 +2416,10 @@
       <c r="A61" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="36" t="s">
+      <c r="B61" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C61" s="37">
+      <c r="C61" s="36">
         <v>4.99</v>
       </c>
     </row>
@@ -2430,10 +2427,10 @@
       <c r="A62" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B62" s="34" t="s">
+      <c r="B62" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C62" s="35">
+      <c r="C62" s="34">
         <v>4.99</v>
       </c>
     </row>
@@ -2441,10 +2438,10 @@
       <c r="A63" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B63" s="38" t="s">
+      <c r="B63" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="C63" s="39">
+      <c r="C63" s="38">
         <v>3.99</v>
       </c>
     </row>
@@ -2452,10 +2449,10 @@
       <c r="A64" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B64" s="40" t="s">
+      <c r="B64" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="C64" s="41">
+      <c r="C64" s="40">
         <v>3.99</v>
       </c>
     </row>
@@ -2463,10 +2460,10 @@
       <c r="A65" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B65" s="42" t="s">
+      <c r="B65" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="C65" s="39">
+      <c r="C65" s="38">
         <v>3.99</v>
       </c>
     </row>
@@ -2474,10 +2471,10 @@
       <c r="A66" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B66" s="40" t="s">
+      <c r="B66" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C66" s="41">
+      <c r="C66" s="40">
         <v>5.99</v>
       </c>
     </row>
@@ -2485,10 +2482,10 @@
       <c r="A67" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B67" s="42" t="s">
+      <c r="B67" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="39">
+      <c r="C67" s="38">
         <v>3.99</v>
       </c>
     </row>
@@ -2496,10 +2493,10 @@
       <c r="A68" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B68" s="43" t="s">
+      <c r="B68" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="44">
+      <c r="C68" s="43">
         <v>7.99</v>
       </c>
     </row>
@@ -2507,10 +2504,10 @@
       <c r="A69" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B69" s="45" t="s">
+      <c r="B69" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="46">
+      <c r="C69" s="45">
         <v>3.99</v>
       </c>
     </row>
@@ -2518,10 +2515,10 @@
       <c r="A70" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B70" s="43" t="s">
+      <c r="B70" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="C70" s="47">
+      <c r="C70" s="46">
         <v>3.99</v>
       </c>
     </row>
@@ -2606,10 +2603,10 @@
       <c r="A78" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B78" s="48" t="s">
+      <c r="B78" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="C78" s="49">
+      <c r="C78" s="48">
         <v>6.49</v>
       </c>
     </row>
@@ -2617,10 +2614,10 @@
       <c r="A79" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B79" s="34" t="s">
+      <c r="B79" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C79" s="50">
+      <c r="C79" s="49">
         <v>6.99</v>
       </c>
     </row>
@@ -2628,10 +2625,10 @@
       <c r="A80" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="36" t="s">
+      <c r="B80" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C80" s="51">
+      <c r="C80" s="50">
         <v>4.99</v>
       </c>
     </row>
@@ -2639,10 +2636,10 @@
       <c r="A81" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B81" s="34" t="s">
+      <c r="B81" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C81" s="50">
+      <c r="C81" s="49">
         <v>4.99</v>
       </c>
     </row>
@@ -2650,10 +2647,10 @@
       <c r="A82" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B82" s="36" t="s">
+      <c r="B82" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C82" s="51">
+      <c r="C82" s="50">
         <v>4.99</v>
       </c>
     </row>
@@ -2661,10 +2658,10 @@
       <c r="A83" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B83" s="34" t="s">
+      <c r="B83" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C83" s="50">
+      <c r="C83" s="49">
         <v>4.99</v>
       </c>
     </row>
@@ -2672,10 +2669,10 @@
       <c r="A84" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B84" s="52" t="s">
+      <c r="B84" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C84" s="53">
+      <c r="C84" s="52">
         <v>5.99</v>
       </c>
     </row>
@@ -2708,7 +2705,7 @@
       <c r="B87" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C87" s="54">
+      <c r="C87" s="53">
         <v>84.99</v>
       </c>
     </row>
@@ -2947,10 +2944,10 @@
       <c r="A109" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B109" s="55" t="s">
+      <c r="B109" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="C109" s="56">
+      <c r="C109" s="55">
         <v>3.99</v>
       </c>
     </row>
@@ -2961,7 +2958,7 @@
       <c r="B110" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="C110" s="57">
+      <c r="C110" s="56">
         <v>5.99</v>
       </c>
     </row>
@@ -2972,7 +2969,7 @@
       <c r="B111" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C111" s="58">
+      <c r="C111" s="57">
         <v>4.99</v>
       </c>
     </row>
@@ -2983,7 +2980,7 @@
       <c r="B112" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="C112" s="57">
+      <c r="C112" s="56">
         <v>0.69</v>
       </c>
     </row>
@@ -2994,7 +2991,7 @@
       <c r="B113" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C113" s="58">
+      <c r="C113" s="57">
         <v>3.99</v>
       </c>
     </row>
@@ -3005,7 +3002,7 @@
       <c r="B114" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C114" s="57">
+      <c r="C114" s="56">
         <v>6.99</v>
       </c>
     </row>
@@ -3016,7 +3013,7 @@
       <c r="B115" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C115" s="58">
+      <c r="C115" s="57">
         <v>4.49</v>
       </c>
     </row>
@@ -3027,7 +3024,7 @@
       <c r="B116" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="C116" s="57">
+      <c r="C116" s="56">
         <v>4.49</v>
       </c>
     </row>
@@ -3038,7 +3035,7 @@
       <c r="B117" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C117" s="58">
+      <c r="C117" s="57">
         <v>4.49</v>
       </c>
     </row>
@@ -3046,10 +3043,10 @@
       <c r="A118" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B118" s="48" t="s">
+      <c r="B118" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="C118" s="59">
+      <c r="C118" s="58">
         <v>4.99</v>
       </c>
     </row>
@@ -3057,10 +3054,10 @@
       <c r="A119" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B119" s="60" t="s">
+      <c r="B119" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="C119" s="61">
+      <c r="C119" s="60">
         <v>6.99</v>
       </c>
     </row>
@@ -3068,10 +3065,10 @@
       <c r="A120" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B120" s="62" t="s">
+      <c r="B120" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="C120" s="63">
+      <c r="C120" s="62">
         <v>6.99</v>
       </c>
     </row>
@@ -3079,10 +3076,10 @@
       <c r="A121" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B121" s="60" t="s">
+      <c r="B121" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="C121" s="61">
+      <c r="C121" s="60">
         <v>6.99</v>
       </c>
     </row>
@@ -3090,10 +3087,10 @@
       <c r="A122" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B122" s="62" t="s">
+      <c r="B122" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="C122" s="63">
+      <c r="C122" s="62">
         <v>8.49</v>
       </c>
     </row>
@@ -3101,10 +3098,10 @@
       <c r="A123" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B123" s="60" t="s">
+      <c r="B123" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="C123" s="61">
+      <c r="C123" s="60">
         <v>7.99</v>
       </c>
     </row>
@@ -3112,10 +3109,10 @@
       <c r="A124" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B124" s="62" t="s">
+      <c r="B124" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="C124" s="63">
+      <c r="C124" s="62">
         <v>7.99</v>
       </c>
     </row>
@@ -3123,10 +3120,10 @@
       <c r="A125" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B125" s="60" t="s">
+      <c r="B125" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="C125" s="61">
+      <c r="C125" s="60">
         <v>7.99</v>
       </c>
     </row>
@@ -3134,10 +3131,10 @@
       <c r="A126" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B126" s="62" t="s">
+      <c r="B126" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="C126" s="63">
+      <c r="C126" s="62">
         <v>14.99</v>
       </c>
     </row>
@@ -3145,10 +3142,10 @@
       <c r="A127" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B127" s="60" t="s">
+      <c r="B127" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="C127" s="61">
+      <c r="C127" s="60">
         <v>3.99</v>
       </c>
     </row>
@@ -3156,10 +3153,10 @@
       <c r="A128" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B128" s="62" t="s">
+      <c r="B128" s="61" t="s">
         <v>190</v>
       </c>
-      <c r="C128" s="63">
+      <c r="C128" s="62">
         <v>7.99</v>
       </c>
     </row>
@@ -3167,10 +3164,10 @@
       <c r="A129" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B129" s="60" t="s">
+      <c r="B129" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C129" s="61">
+      <c r="C129" s="60">
         <v>3.99</v>
       </c>
     </row>
@@ -3178,10 +3175,10 @@
       <c r="A130" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B130" s="62" t="s">
+      <c r="B130" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="C130" s="63">
+      <c r="C130" s="62">
         <v>2.99</v>
       </c>
     </row>
@@ -3189,10 +3186,10 @@
       <c r="A131" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B131" s="60" t="s">
+      <c r="B131" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="C131" s="61">
+      <c r="C131" s="60">
         <v>2.99</v>
       </c>
     </row>
@@ -3200,10 +3197,10 @@
       <c r="A132" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B132" s="62" t="s">
+      <c r="B132" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="C132" s="63">
+      <c r="C132" s="62">
         <v>5.59</v>
       </c>
     </row>
@@ -3211,10 +3208,10 @@
       <c r="A133" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B133" s="60" t="s">
+      <c r="B133" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="C133" s="61">
+      <c r="C133" s="60">
         <v>2.59</v>
       </c>
     </row>
@@ -3222,10 +3219,10 @@
       <c r="A134" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B134" s="62" t="s">
+      <c r="B134" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="C134" s="63">
+      <c r="C134" s="62">
         <v>2.59</v>
       </c>
     </row>
@@ -3233,10 +3230,10 @@
       <c r="A135" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B135" s="60" t="s">
+      <c r="B135" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="C135" s="61">
+      <c r="C135" s="60">
         <v>2.59</v>
       </c>
     </row>
@@ -3244,10 +3241,10 @@
       <c r="A136" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B136" s="62" t="s">
+      <c r="B136" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="C136" s="63">
+      <c r="C136" s="62">
         <v>2.59</v>
       </c>
     </row>
@@ -3255,10 +3252,10 @@
       <c r="A137" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B137" s="60" t="s">
+      <c r="B137" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="C137" s="61">
+      <c r="C137" s="60">
         <v>2.59</v>
       </c>
     </row>
@@ -3266,10 +3263,10 @@
       <c r="A138" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B138" s="62" t="s">
+      <c r="B138" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="C138" s="63">
+      <c r="C138" s="62">
         <v>2.59</v>
       </c>
     </row>
@@ -3277,10 +3274,10 @@
       <c r="A139" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B139" s="60" t="s">
+      <c r="B139" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="C139" s="61">
+      <c r="C139" s="60">
         <v>2.59</v>
       </c>
     </row>
@@ -3288,10 +3285,10 @@
       <c r="A140" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B140" s="62" t="s">
+      <c r="B140" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="C140" s="63">
+      <c r="C140" s="62">
         <v>2.59</v>
       </c>
     </row>
@@ -3299,10 +3296,10 @@
       <c r="A141" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B141" s="60" t="s">
+      <c r="B141" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="C141" s="61">
+      <c r="C141" s="60">
         <v>3.99</v>
       </c>
     </row>
@@ -3310,10 +3307,10 @@
       <c r="A142" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B142" s="62" t="s">
+      <c r="B142" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="C142" s="63">
+      <c r="C142" s="62">
         <v>2.59</v>
       </c>
     </row>
@@ -3321,10 +3318,10 @@
       <c r="A143" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B143" s="60" t="s">
+      <c r="B143" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="C143" s="61">
+      <c r="C143" s="60">
         <v>2.59</v>
       </c>
     </row>
@@ -3332,10 +3329,10 @@
       <c r="A144" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B144" s="62" t="s">
+      <c r="B144" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="C144" s="63">
+      <c r="C144" s="62">
         <v>1.99</v>
       </c>
     </row>
@@ -3343,10 +3340,10 @@
       <c r="A145" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B145" s="60" t="s">
+      <c r="B145" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="C145" s="61">
+      <c r="C145" s="60">
         <v>2.59</v>
       </c>
     </row>
@@ -3354,10 +3351,10 @@
       <c r="A146" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B146" s="62" t="s">
+      <c r="B146" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="C146" s="63">
+      <c r="C146" s="62">
         <v>2.59</v>
       </c>
     </row>
@@ -3365,10 +3362,10 @@
       <c r="A147" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B147" s="60" t="s">
+      <c r="B147" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="C147" s="61">
+      <c r="C147" s="60">
         <v>2.59</v>
       </c>
     </row>
@@ -3376,10 +3373,10 @@
       <c r="A148" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B148" s="62" t="s">
+      <c r="B148" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="C148" s="63">
+      <c r="C148" s="62">
         <v>1.99</v>
       </c>
     </row>
@@ -3387,10 +3384,10 @@
       <c r="A149" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B149" s="60" t="s">
+      <c r="B149" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="C149" s="61">
+      <c r="C149" s="60">
         <v>2.59</v>
       </c>
     </row>
@@ -3398,10 +3395,10 @@
       <c r="A150" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B150" s="62" t="s">
+      <c r="B150" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="C150" s="63">
+      <c r="C150" s="62">
         <v>1.99</v>
       </c>
     </row>
@@ -3409,10 +3406,10 @@
       <c r="A151" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B151" s="60" t="s">
+      <c r="B151" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="C151" s="61">
+      <c r="C151" s="60">
         <v>1.99</v>
       </c>
     </row>
@@ -3420,10 +3417,10 @@
       <c r="A152" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B152" s="62" t="s">
+      <c r="B152" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="C152" s="63">
+      <c r="C152" s="62">
         <v>4.99</v>
       </c>
     </row>
@@ -3431,10 +3428,10 @@
       <c r="A153" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B153" s="60" t="s">
+      <c r="B153" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="C153" s="61">
+      <c r="C153" s="60">
         <v>5.99</v>
       </c>
     </row>
@@ -3442,10 +3439,10 @@
       <c r="A154" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B154" s="62" t="s">
+      <c r="B154" s="61" t="s">
         <v>89</v>
       </c>
-      <c r="C154" s="63">
+      <c r="C154" s="62">
         <v>2.59</v>
       </c>
     </row>
@@ -3453,10 +3450,10 @@
       <c r="A155" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B155" s="60" t="s">
+      <c r="B155" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C155" s="61">
+      <c r="C155" s="60">
         <v>2.59</v>
       </c>
     </row>
@@ -3464,10 +3461,10 @@
       <c r="A156" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B156" s="64" t="s">
+      <c r="B156" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="C156" s="65">
+      <c r="C156" s="64">
         <v>2.59</v>
       </c>
     </row>
@@ -3475,10 +3472,10 @@
       <c r="A157" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B157" s="66" t="s">
+      <c r="B157" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="C157" s="67">
+      <c r="C157" s="66">
         <v>11.99</v>
       </c>
     </row>
@@ -3486,10 +3483,10 @@
       <c r="A158" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B158" s="68" t="s">
+      <c r="B158" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="C158" s="69">
+      <c r="C158" s="68">
         <v>4.99</v>
       </c>
     </row>
@@ -3497,10 +3494,10 @@
       <c r="A159" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B159" s="70" t="s">
+      <c r="B159" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="C159" s="71">
+      <c r="C159" s="70">
         <v>2.99</v>
       </c>
     </row>
@@ -3508,10 +3505,10 @@
       <c r="A160" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B160" s="72" t="s">
+      <c r="B160" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="C160" s="72">
+      <c r="C160" s="71">
         <v>4.99</v>
       </c>
     </row>
@@ -3519,10 +3516,10 @@
       <c r="A161" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B161" s="70" t="s">
+      <c r="B161" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="C161" s="71">
+      <c r="C161" s="70">
         <v>4.49</v>
       </c>
     </row>
@@ -3530,10 +3527,10 @@
       <c r="A162" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B162" s="68" t="s">
+      <c r="B162" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C162" s="69">
+      <c r="C162" s="68">
         <v>3.49</v>
       </c>
     </row>
@@ -3541,10 +3538,10 @@
       <c r="A163" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B163" s="70" t="s">
+      <c r="B163" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="C163" s="71">
+      <c r="C163" s="70">
         <v>2.4900000000000002</v>
       </c>
     </row>
@@ -3552,10 +3549,10 @@
       <c r="A164" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B164" s="73" t="s">
+      <c r="B164" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="C164" s="69">
+      <c r="C164" s="68">
         <v>3.99</v>
       </c>
     </row>
@@ -3563,10 +3560,10 @@
       <c r="A165" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B165" s="74" t="s">
+      <c r="B165" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="C165" s="71">
+      <c r="C165" s="70">
         <v>3.99</v>
       </c>
     </row>
@@ -3574,10 +3571,10 @@
       <c r="A166" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B166" s="73" t="s">
+      <c r="B166" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="C166" s="69">
+      <c r="C166" s="68">
         <v>4.99</v>
       </c>
     </row>
@@ -3585,10 +3582,10 @@
       <c r="A167" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B167" s="74" t="s">
+      <c r="B167" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="C167" s="71">
+      <c r="C167" s="70">
         <v>2.99</v>
       </c>
     </row>
@@ -3596,10 +3593,10 @@
       <c r="A168" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B168" s="68" t="s">
+      <c r="B168" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="C168" s="69">
+      <c r="C168" s="68">
         <v>3.99</v>
       </c>
     </row>
@@ -3607,10 +3604,10 @@
       <c r="A169" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B169" s="70" t="s">
+      <c r="B169" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="C169" s="71">
+      <c r="C169" s="70">
         <v>2.99</v>
       </c>
     </row>
@@ -3618,10 +3615,10 @@
       <c r="A170" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B170" s="68" t="s">
+      <c r="B170" s="67" t="s">
         <v>105</v>
       </c>
-      <c r="C170" s="69">
+      <c r="C170" s="68">
         <v>7.99</v>
       </c>
     </row>
@@ -3629,10 +3626,10 @@
       <c r="A171" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B171" s="70" t="s">
+      <c r="B171" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="C171" s="71">
+      <c r="C171" s="70">
         <v>1.99</v>
       </c>
     </row>
@@ -3640,10 +3637,10 @@
       <c r="A172" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B172" s="68" t="s">
+      <c r="B172" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="C172" s="69">
+      <c r="C172" s="68">
         <v>1.99</v>
       </c>
     </row>
@@ -3651,10 +3648,10 @@
       <c r="A173" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B173" s="70" t="s">
+      <c r="B173" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="C173" s="71">
+      <c r="C173" s="70">
         <v>4.49</v>
       </c>
     </row>
@@ -3662,10 +3659,10 @@
       <c r="A174" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B174" s="68" t="s">
+      <c r="B174" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="C174" s="69">
+      <c r="C174" s="68">
         <v>4.49</v>
       </c>
     </row>
@@ -3673,10 +3670,10 @@
       <c r="A175" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B175" s="70" t="s">
+      <c r="B175" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="C175" s="71">
+      <c r="C175" s="70">
         <v>3.49</v>
       </c>
     </row>
@@ -3684,10 +3681,10 @@
       <c r="A176" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B176" s="68" t="s">
+      <c r="B176" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="C176" s="69">
+      <c r="C176" s="68">
         <v>5.99</v>
       </c>
     </row>
@@ -3695,10 +3692,10 @@
       <c r="A177" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B177" s="70" t="s">
+      <c r="B177" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="C177" s="71">
+      <c r="C177" s="70">
         <v>6.99</v>
       </c>
     </row>
@@ -3706,10 +3703,10 @@
       <c r="A178" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B178" s="75" t="s">
+      <c r="B178" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="C178" s="76">
+      <c r="C178" s="75">
         <v>4.99</v>
       </c>
     </row>
@@ -3739,7 +3736,7 @@
       <c r="A181" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B181" s="77" t="s">
+      <c r="B181" s="76" t="s">
         <v>194</v>
       </c>
       <c r="C181" s="26">
